--- a/assets/constructions/examples/ctd_mie_t.xlsx
+++ b/assets/constructions/examples/ctd_mie_t.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,11 +594,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSTF90-D80-32-8-120-10</t>
+          <t>DMKF90-D80-32-3-24-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -608,7 +628,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DSTF90</t>
+          <t>DMKF90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -622,43 +642,43 @@
       <c r="H2" t="n">
         <v>120</v>
       </c>
-      <c r="I2" t="n">
-        <v>45</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SPMG06</t>
+          <t>MGMN3</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HB-32</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>LIKON_SP0602H</t>
+          <t>LIKON_MG3</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -668,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -676,12 +696,10 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>31.5</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>LIK_SP0602H</t>
+          <t>LIK_MG3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -691,11 +709,17 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DMKF90-D55-25-5-15-2</t>
+          <t>DMKF90-D63-25-4-19-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -710,7 +734,7 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
@@ -728,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -736,7 +760,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -745,7 +769,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MGMN5</t>
+          <t>MGMN4</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,7 +779,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>LIKON_MG5</t>
+          <t>LIKON_MG4</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -776,7 +800,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>LIK_MG5</t>
+          <t>LIK_MG4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -786,52 +810,68 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSTF90-D63-32-5-120-8</t>
+          <t>12290901200</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DSTF90</t>
+          <t>M94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="F4" t="n">
+        <v>65</v>
+      </c>
       <c r="G4" t="n">
         <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.26</v>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -840,7 +880,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SPMG05</t>
+          <t>TNAX1604ZZ..</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,7 +890,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>LIKON_SP0502H</t>
+          <t>WIDIA_TNAX1604H</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -860,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -869,25 +909,37 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>LIK_SP0502H</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+          <t>WID_TNAX1604_H</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>WID_TNAX16_X2</t>
+        </is>
+      </c>
+      <c r="AF4" t="b">
+        <v>1</v>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2019 /Novo</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12290900800</t>
+          <t>12391602600M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -897,48 +949,44 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M94</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>25</v>
       </c>
-      <c r="F5" t="n">
-        <v>34</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.73</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="S5" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -947,17 +995,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>TCAX1103ZZ..</t>
+          <t>CPNT060204T</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>HB-25</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>WIDIA_TCAX1103H</t>
+          <t>WIDIA_CP0602H</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -967,40 +1015,46 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
         <v>3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>WID_CP0602_H</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>WID_123916_3408</t>
+        </is>
+      </c>
+      <c r="AF5" t="b">
         <v>0</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>WID_TCAX1103_H</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>WID_TCAX11_X1</t>
-        </is>
-      </c>
-      <c r="AF5" t="b">
-        <v>1</v>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2019 /Novo</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DMKF90-D50-25-4-12-2</t>
+          <t>DCGF90-D25-20-11-100-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1010,38 +1064,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DMKF90</t>
+          <t>DSGF90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>120</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
         <v>4</v>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1050,17 +1104,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>MGMN4</t>
+          <t>CCMT0602</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>LIKON_MG4</t>
+          <t>ISO_CC0602H</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1078,10 +1132,12 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>15</v>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>LIK_MG4</t>
+          <t>CC0602H</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1091,6 +1147,12 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
